--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:09</t>
+    <t xml:space="preserve">2026-09-09 23:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:03</t>
+    <t xml:space="preserve">2026-09-17 14:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:00</t>
+    <t xml:space="preserve">2026-09-23 12:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1500,7 +1500,9 @@
       <c r="C53" s="2" t="n">
         <v>13303</v>
       </c>
-      <c r="D53" s="2"/>
+      <c r="D53" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E53" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:30</t>
+    <t xml:space="preserve">2026-10-02 14:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:18</t>
+    <t xml:space="preserve">2026-10-05 10:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -654,7 +654,7 @@
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2028697.62</v>
+        <v>2028697.63</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +671,7 @@
         <v>2021</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1903789.12</v>
+        <v>1903789.13</v>
       </c>
     </row>
     <row r="5">
@@ -688,7 +688,7 @@
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1816561.12</v>
+        <v>1816561.13</v>
       </c>
     </row>
     <row r="6">
@@ -807,7 +807,7 @@
         <v>2021</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1058416.12</v>
+        <v>1058416.13</v>
       </c>
     </row>
     <row r="13">
@@ -875,7 +875,7 @@
         <v>2021</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>986148.12</v>
+        <v>986148.13</v>
       </c>
     </row>
     <row r="17">
@@ -926,7 +926,7 @@
         <v>2021</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>963317.12</v>
+        <v>963317.13</v>
       </c>
     </row>
     <row r="20">
@@ -1181,7 +1181,7 @@
         <v>2021</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>796662.12</v>
+        <v>796662.13</v>
       </c>
     </row>
     <row r="35">
